--- a/resources/residence/residence_entry.xlsx
+++ b/resources/residence/residence_entry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="District" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidenceEntry" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StateCountConfig" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="State" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="District" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ResidenceEntry" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="StateCountConfig" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">State!#REF!</definedName>
@@ -2061,7 +2061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -2284,38 +2284,34 @@
     </row>
     <row r="9" ht="16.5" customHeight="1" s="8">
       <c r="A9" s="15" t="n">
-        <v>10201</v>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>乙丑洞</t>
+        <v>10150</v>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>灵泉谷入口</t>
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>30001</v>
+        <v>30010</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>8028</v>
+        <v>8040</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>8008</v>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>Main_R_G_0_1003</t>
-        </is>
-      </c>
+        <v>8010</v>
+      </c>
+      <c r="H9" s="22" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="8">
       <c r="A10" s="15" t="n">
-        <v>10202</v>
+        <v>10201</v>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>乙未洞</t>
+          <t>乙丑洞</t>
         </is>
       </c>
       <c r="D10" s="12" t="n">
@@ -2332,17 +2328,17 @@
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>Main_R_G_0_1004</t>
+          <t>Main_R_G_0_1003</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="8">
       <c r="A11" s="15" t="n">
-        <v>10203</v>
+        <v>10202</v>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>乙卯洞</t>
+          <t>乙未洞</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
@@ -2357,23 +2353,23 @@
       <c r="G11" s="12" t="n">
         <v>8008</v>
       </c>
-      <c r="H11" s="22" t="inlineStr">
-        <is>
-          <t>Main_R_G_0_1010</t>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>Main_R_G_0_1004</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="8">
       <c r="A12" s="15" t="n">
-        <v>20101</v>
+        <v>10203</v>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>戊戌洞</t>
+          <t>乙卯洞</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>30001</v>
@@ -2384,19 +2380,19 @@
       <c r="G12" s="12" t="n">
         <v>8008</v>
       </c>
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>Main_R_G_0_1005</t>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>Main_R_G_0_1010</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="8">
       <c r="A13" s="15" t="n">
-        <v>20102</v>
+        <v>20101</v>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>戊午洞</t>
+          <t>戊戌洞</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
@@ -2413,17 +2409,17 @@
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>Main_R_G_0_1006</t>
+          <t>Main_R_G_0_1005</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="8">
       <c r="A14" s="15" t="n">
-        <v>20103</v>
+        <v>20102</v>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>戊申洞</t>
+          <t>戊午洞</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
@@ -2438,23 +2434,23 @@
       <c r="G14" s="12" t="n">
         <v>8008</v>
       </c>
-      <c r="H14" s="22" t="inlineStr">
-        <is>
-          <t>Main_R_G_0_1011</t>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>Main_R_G_0_1006</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="8">
       <c r="A15" s="15" t="n">
-        <v>20201</v>
+        <v>20103</v>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>癸酉洞</t>
+          <t>戊申洞</t>
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>30001</v>
@@ -2465,19 +2461,19 @@
       <c r="G15" s="12" t="n">
         <v>8008</v>
       </c>
-      <c r="H15" s="0" t="inlineStr">
-        <is>
-          <t>Main_R_G_0_1007</t>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>Main_R_G_0_1011</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="8">
       <c r="A16" s="15" t="n">
-        <v>20202</v>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>癸卯洞</t>
+        <v>20201</v>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>癸酉洞</t>
         </is>
       </c>
       <c r="D16" s="12" t="n">
@@ -2494,17 +2490,17 @@
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>Main_R_G_0_1008</t>
+          <t>Main_R_G_0_1007</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>20203</v>
+        <v>20202</v>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>癸未洞</t>
+          <t>癸卯洞</t>
         </is>
       </c>
       <c r="D17" s="12" t="n">
@@ -2519,7 +2515,34 @@
       <c r="G17" s="12" t="n">
         <v>8008</v>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>Main_R_G_0_1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>20203</v>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>癸未洞</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>202</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>30001</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>8028</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>8008</v>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>Main_R_G_0_1012</t>
         </is>
